--- a/inst/app/metadata/snakamura2_2024-08-30.xlsx
+++ b/inst/app/metadata/snakamura2_2024-08-30.xlsx
@@ -1,24 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/innovation_hub/InnovationHubDashboard/inst/app/metadata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_0C68FDCE8F79A89360642C52EAAA9A77E4F6DD47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017CB5D9-DD08-4B12-90E8-B7DB2E0E0158}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="25080" yWindow="-540" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>authors</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>paper_url</t>
+  </si>
+  <si>
+    <t>paper_publish_date</t>
+  </si>
+  <si>
+    <t>keywords</t>
+  </si>
+  <si>
+    <t>pip_vintage_primary_data</t>
+  </si>
+  <si>
+    <t>economy_excl_reason</t>
+  </si>
+  <si>
+    <t>aggregates_excl_reason</t>
+  </si>
+  <si>
+    <t>limitations</t>
+  </si>
+  <si>
+    <t>citation</t>
+  </si>
+  <si>
+    <t>Where Is Poverty Concentrated ? New Evidence Based on Internationally Consistent Urban and Poverty Measurements</t>
+  </si>
+  <si>
+    <t>(Shohei Nakamura, World Bank, snakamura2@worldbank.org); (Pierre-Philippe Combes, Sciences Po; pierrephilippe.combes@scie_x000D_
+ncespo.fr) (Robin Moellerherm, Heidelberg University; robin.moellerherm@awi.uni-heidelberg.de) (Charlotte Robert, Heidelberg_x000D_
+University; charlotte.robert@awi.uni-heidelberg.de) (Mark Roberts, World Bank; mroberts1@worldbank.org) (Benjamin Stewart, World Bank; bstewart@worldbankgroup.org) (Slava Yakubenko, Westminster International University in Tashkent and_x000D_
+HSE University; viacheslav.yakubenko@wiwi.uni-goettingen.de)</t>
+  </si>
+  <si>
+    <t>The data was produced by applying globally consistent urban measurement approaches (Degree of Urbanization and Dartboard) to household budget survey datasets to disaggregate global poverty into comparable urban and rural areas. Spatial deflators were also updated based on the new geographic classifications.</t>
+  </si>
+  <si>
+    <t>https://documents.worldbank.org/en/publication/documents-reports/documentdetail/099823311272312886/idu047ac48f0062ea04222098780cda70c42240d</t>
+  </si>
+  <si>
+    <t>Global poverty; urban poverty; urbanization; cost of living; Sub-Saharan Africa</t>
+  </si>
+  <si>
+    <t>not known</t>
+  </si>
+  <si>
+    <t>Countries are selected based on data availability</t>
+  </si>
+  <si>
+    <t>Nakamura,Shohei; Combes,Pierre Philippe; Moellerherm,Robin; Robert,Charlotte Genevieve Julka; Roberts,Mark; Stewart,Benjamin; Yakubenko,Slava._x000D_
+Where Is Poverty Concentrated ? New Evidence Based on Internationally Consistent Urban and Poverty Measurements (English). Policy Research working paper ; no. WPS 10620 Washington, D.C. : World Bank Group.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -30,6 +102,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -52,28 +132,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -111,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -145,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -179,9 +271,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -354,120 +447,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>authors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>paper_url</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>paper_publish_date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>keywords</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pip_vintage_primary_data</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>economy_excl_reason</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>aggregates_excl_reason</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>limitations</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Where Is Poverty Concentrated ? New Evidence Based on Internationally Consistent Urban and Poverty Measurements</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>(Shohei Nakamura, World Bank, snakamura2@worldbank.org); (Pierre-Philippe Combes, Sciences Po; pierrephilippe.combes@scie_x000D_
-ncespo.fr) (Robin Moellerherm, Heidelberg University; robin.moellerherm@awi.uni-heidelberg.de) (Charlotte Robert, Heidelberg_x000D_
-University; charlotte.robert@awi.uni-heidelberg.de) (Mark Roberts, World Bank; mroberts1@worldbank.org) (Benjamin Stewart, World Bank; bstewart@worldbankgroup.org) (Slava Yakubenko, Westminster International University in Tashkent and_x000D_
-HSE University; viacheslav.yakubenko@wiwi.uni-goettingen.de)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The data was produced by applying globally consistent urban measurement approaches (Degree of Urbanization and Dartboard) to household budget survey datasets to disaggregate global poverty into comparable urban and rural areas. Spatial deflators were also updated based on the new geographic classifications.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://documents.worldbank.org/en/publication/documents-reports/documentdetail/099823311272312886/idu047ac48f0062ea04222098780cda70c42240d</t>
-        </is>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E2" s="2">
         <v>45257</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Global poverty; urban poverty; urbanization; cost of living; Sub-Saharan Africa</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>not known</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Countries are selected based on data availability</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Nakamura,Shohei; Combes,Pierre Philippe; Moellerherm,Robin; Robert,Charlotte Genevieve Julka; Roberts,Mark; Stewart,Benjamin; Yakubenko,Slava._x000D_
-Where Is Poverty Concentrated ? New Evidence Based on Internationally Consistent Urban and Poverty Measurements (English). Policy Research working paper ; no. WPS 10620 Washington, D.C. : World Bank Group.</t>
-        </is>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{1D5B6E50-D2B7-4A6D-BFA3-DBA848C0A89F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>